--- a/sources/jun_step7.xlsx
+++ b/sources/jun_step7.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA110"/>
+  <dimension ref="A1:AB110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="105" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>562fca0e-a7ac-490f-9c30-94bc0669d5f7</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>8d055b95-dd7a-406f-bd06-15b694e42e7e</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>ac608881-4c14-492a-95a0-bb84457dee71</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>baeef81a-3f0b-4a74-b979-3d2e6227b532</t>
         </is>
@@ -783,12 +789,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>9d0ebd20-abbf-45b1-865b-3eb5298dad00</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>54c315de-f3ea-477f-91d0-0c1229be9967</t>
         </is>
@@ -797,22 +803,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>b+1+2 [~5]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>b+1+2 [~5]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cherry Blossom [Tag]</t>
+          <t>Cherry Blossom</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cherry Blossom [Tag]</t>
+          <t>Cherry Blossom</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -857,10 +863,15 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
           <t>e60a86ac-41e7-40bd-bb88-5f769aaf3596</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>d3d774f0-43b0-4e4f-a70a-16400e3f8b7a</t>
         </is>
@@ -917,12 +928,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>c3fb2b44-9abc-4fc9-8f10-b2e01504275a</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -979,12 +990,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4e122e09-243f-49b9-96ea-c109b7d9a02f</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1041,12 +1052,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>30e2beaa-6d7c-42d2-8397-096837f7826d</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1178,20 +1189,25 @@
       </c>
       <c r="X12" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y12" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y12" s="1" t="inlineStr">
+      <c r="Z12" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z12" s="1" t="inlineStr">
+      <c r="AA12" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA12" s="1" t="inlineStr">
+      <c r="AB12" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1273,12 +1289,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>a67acfcf-2688-4ee4-bc20-044349e8e7c8</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>3f35d390-6837-4fa5-8a62-ec15c6ba282b</t>
         </is>
@@ -1360,12 +1376,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>1b96f902-1494-48c1-b8f9-572e9de9e458</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>4ad37f5e-ddad-4e2b-8684-89afb757ddff</t>
         </is>
@@ -1447,12 +1463,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>9b493e6e-af04-48e5-8c67-6f27753b11b7</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>8b7bdac3-69b3-4f99-8c4d-5efec59f9fec</t>
         </is>
@@ -1534,12 +1550,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>73d7d147-4681-4164-bbff-247040d25edc</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>b7baea7b-7ce7-4b47-8673-a793c2d621b0</t>
         </is>
@@ -1621,12 +1637,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>2662fd1d-49ce-404b-8300-ba2ad5badde0</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>45e92277-8e60-4f97-ba70-8a212d38ddda</t>
         </is>
@@ -1708,12 +1724,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>fcc2d5d3-c1de-4f49-a313-6fb76130d9ea</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>e17c9656-9d57-4661-8452-778513b52d0b</t>
         </is>
@@ -1795,12 +1811,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>220aec40-dc80-4989-bc76-b639356960c1</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>80ad047c-55ce-4ab3-bca4-2a33a658419f</t>
         </is>
@@ -1882,12 +1898,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>ca388b08-a891-4b69-807e-215b2ce5e80b</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>2a40c56a-a9d5-4f6a-b4ba-e839bc2e5dab</t>
         </is>
@@ -1969,12 +1985,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>84327d77-2ddd-4677-aab7-6bd625b73f34</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>8c83e259-e453-48b8-97af-66ee398c2264</t>
         </is>
@@ -2056,12 +2072,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>429ff6ff-8b36-455a-961c-bb38c39394fe</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>4545c166-8606-4878-b44d-55c133c05309</t>
         </is>
@@ -2143,12 +2159,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>63974d60-04b8-4245-abb7-839810f09d03</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>8ad70b8c-0622-48ac-b990-c71a1f196960</t>
         </is>
@@ -2230,12 +2246,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>9671898d-db41-4c1a-ba25-7b69894aeff3</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>35998383-2f42-460c-8963-6c520f4fc12c</t>
         </is>
@@ -2317,12 +2333,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>1ed0d25c-bd4b-4e99-ad4d-4d6d589b723d</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>67f4f9b5-8dbb-46e7-91c2-9f40692ca62c</t>
         </is>
@@ -2404,12 +2420,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>c1fbc72f-a01e-4042-b8d6-b7acaad0fe53</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>4497c2e1-1891-4f68-9fef-de01c0799cdd</t>
         </is>
@@ -2491,12 +2507,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>9b6cd032-0799-4453-b6aa-f148a302d8ea</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>7a333992-970a-4c33-a226-44b47034151b</t>
         </is>
@@ -2578,12 +2594,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>4e56b404-118b-4ed7-90e0-697e225129e8</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>ca1d048b-e843-452f-8c2f-4a277767d7c8</t>
         </is>
@@ -2665,12 +2681,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>fae7b64a-4139-44db-a483-e35944382b50</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>9d7b5edc-2b84-47f9-84f1-a545f8030bf6</t>
         </is>
@@ -2752,12 +2768,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>74cdbe65-1314-4803-94cc-b6468c375eb2</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>e4d86eb6-c329-4102-9058-b856202058ec</t>
         </is>
@@ -2839,12 +2855,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>a2209524-18b6-47f3-8cae-4898eca5eff3</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>fe026fa1-c7b7-455b-a31d-1c0df35a413e</t>
         </is>
@@ -2926,12 +2942,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>6c598c10-056f-4fbc-b851-94cf429b0009</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>1e6958eb-930f-4466-b80b-ed4c6d483212</t>
         </is>
@@ -3013,12 +3029,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>8481a795-c52b-4a3c-8f0c-69054d66bab1</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>f76c37e2-8175-4d8a-a390-37659632f7c8</t>
         </is>
@@ -3100,12 +3116,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>69c800ae-22f9-48ab-b1b2-464fdffc34f2</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>ea356187-6f84-4589-b977-72b26e3f424a</t>
         </is>
@@ -3187,12 +3203,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>3dff0274-576a-4c03-b8e6-440eaaf84c07</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>f44a3bed-779f-41b4-a4ae-993bf47bdd54</t>
         </is>
@@ -3274,12 +3290,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>2f11fd8f-74c0-44bd-bdf3-bbac9698a2de</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>41026480-4fdd-4cc1-aa6e-5de47aa5cf61</t>
         </is>
@@ -3411,20 +3427,25 @@
       </c>
       <c r="X39" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y39" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y39" s="1" t="inlineStr">
+      <c r="Z39" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z39" s="1" t="inlineStr">
+      <c r="AA39" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA39" s="1" t="inlineStr">
+      <c r="AB39" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3521,12 +3542,12 @@
           <t>MS</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>8fca840a-0cb0-41a1-a047-1fb234f8c237</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>450c889c-b2fa-4ac8-b4ac-c668b04bdc6c</t>
         </is>
@@ -3618,12 +3639,12 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>a9659884-1ec9-49ea-97f6-adf07a1a4948</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>8ea9ab41-8b3e-4d24-9389-e5c995776885</t>
         </is>
@@ -3715,17 +3736,17 @@
           <t>Continue with the White Heron Series extentions.</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>85d4744a-b69b-4589-a737-5465bf91a087</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>e8471969-4dc9-4ed8-83b8-b537bb1093a8</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>a9659884-1ec9-49ea-97f6-adf07a1a4948</t>
         </is>
@@ -3812,17 +3833,17 @@
           <t>mmh</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>1b947dab-c943-46f7-b526-99be45bbf78e</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>90784cfa-53fc-4e9a-bd84-2703cecfdcca</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>a9659884-1ec9-49ea-97f6-adf07a1a4948</t>
         </is>
@@ -3914,17 +3935,17 @@
           <t>Continue with the Front Kick Series extentions.</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>641fa263-1b73-4b0b-b79c-48bfae187501</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>bfc82120-3b8b-47af-8702-e0267a7bac7c</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr">
         <is>
           <t>1b947dab-c943-46f7-b526-99be45bbf78e</t>
         </is>
@@ -4016,17 +4037,17 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>c23abd46-0989-4f7f-bdc4-b9b70cfcd797</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>df6982d4-d04f-44f4-9166-68fa5f73fa13</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>1b947dab-c943-46f7-b526-99be45bbf78e</t>
         </is>
@@ -4113,17 +4134,17 @@
           <t>mmhm</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>87b57283-2995-44ba-ad6f-1e635f8774bd</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>4663ad7f-d965-4f92-9fd7-28b9bf8ee59b</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr">
         <is>
           <t>1b947dab-c943-46f7-b526-99be45bbf78e</t>
         </is>
@@ -4210,17 +4231,17 @@
           <t>mmhl</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>4cfaeb0c-0ac7-4db4-b0d6-11f52dcc734f</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>2978a3df-5d32-4d6b-8a59-7859866e34c7</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr">
         <is>
           <t>1b947dab-c943-46f7-b526-99be45bbf78e</t>
         </is>
@@ -4312,17 +4333,17 @@
           <t>Continue with the Leg Cutter Series extentions.; Hold down to recover crouching.</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>16116a37-e667-4ecf-b256-99176c424d11</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>9ee39938-59f1-47f1-a7da-fc63b5b9faad</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>1b947dab-c943-46f7-b526-99be45bbf78e</t>
         </is>
@@ -4419,12 +4440,12 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>db70867a-fd30-4b9e-8e15-2499e10e0401</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>367dae6d-2471-40f2-9051-cf01bbaaad4d</t>
         </is>
@@ -4516,12 +4537,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>a33d82a2-e2b7-4310-8bc0-2101626aef8d</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>323c1ded-b89b-4851-8582-e5392eea98b0</t>
         </is>
@@ -4613,12 +4634,12 @@
           <t>hl</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>d73b62e9-2689-4ec9-9731-3efe42e12d72</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>35924d25-a0a0-4197-9eba-1fb162bfad82</t>
         </is>
@@ -4715,12 +4736,12 @@
           <t>Continue with the Leg Cutter Series extentions.; Hold down to recover crouching.</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>bc1372a3-c0df-42a5-aa2e-f999daae21aa</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>4816ab33-0984-45db-bd4c-56962d128185</t>
         </is>
@@ -4817,12 +4838,12 @@
           <t>Continue with the Front Kick Series extentions.</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>7a8c5058-2643-42db-b509-a7304138f212</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>a9678676-711d-4025-bccc-03a4cdaf29d4</t>
         </is>
@@ -4914,17 +4935,17 @@
           <t>Continue with the Front Kick Series extentions.</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>1927f3c0-25a6-424c-8405-6fc260a33028</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>d5b25b22-6abf-4c1b-b7a8-1f181a8ec612</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>7a8c5058-2643-42db-b509-a7304138f212</t>
         </is>
@@ -5016,17 +5037,17 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>0f5bfee9-1d7b-427d-96d0-ba85b23cab1d</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>025ebf40-ed86-4303-ab06-ce6308b1f1f4</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr">
         <is>
           <t>7a8c5058-2643-42db-b509-a7304138f212</t>
         </is>
@@ -5083,12 +5104,12 @@
           <t>Throws on a counter hit. Damage is 22.</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>6b2edeb1-01d1-448f-bc16-90d4f3f972a1</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>8c88efae-e7bc-49b2-8219-6d4cd5cf6bc8</t>
         </is>
@@ -5185,12 +5206,12 @@
           <t>JG CF</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>eb065c24-aefe-49c2-b5c8-3beb1981a3ea</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>06ad7695-d9b8-4036-9c73-8b769981000d</t>
         </is>
@@ -5282,12 +5303,12 @@
           <t>sh</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>5e1095fd-8d25-4f57-8c16-4ee0450376a6</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>ad3dc52b-f761-4955-8e85-ad63e0947bdc</t>
         </is>
@@ -5374,17 +5395,17 @@
           <t>shm</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>c1e91929-0ccc-49ec-8a63-2b5876d46060</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>36d0a05b-d60b-4f3f-bb99-4c40794b3093</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>5e1095fd-8d25-4f57-8c16-4ee0450376a6</t>
         </is>
@@ -5476,17 +5497,17 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>1582c3cb-5379-47ae-8c1b-16527159445c</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>dce7b13a-0d70-4884-a515-154eae3eadf9</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>5e1095fd-8d25-4f57-8c16-4ee0450376a6</t>
         </is>
@@ -5573,17 +5594,17 @@
           <t>shh</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>c4b1e1c8-3af0-4a69-bebd-86be82bc2f76</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>36ce126d-6cbc-48fe-97ca-860bd82b50c8</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr">
         <is>
           <t>5e1095fd-8d25-4f57-8c16-4ee0450376a6</t>
         </is>
@@ -5670,17 +5691,17 @@
           <t>shhm</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>8af0cd2f-45f2-4052-9372-f619bf793e9e</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>a815ad96-df04-4047-b9a9-17a64f27ff40</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr">
         <is>
           <t>c4b1e1c8-3af0-4a69-bebd-86be82bc2f76</t>
         </is>
@@ -5767,17 +5788,17 @@
           <t>shhl</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>7922ac19-d90d-4f7d-9f50-2e93c3c8209a</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>117a5cd3-314f-4444-86b8-797ae2402457</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>c4b1e1c8-3af0-4a69-bebd-86be82bc2f76</t>
         </is>
@@ -5869,17 +5890,17 @@
           <t>Continue with the Leg Cutter Series extentions.; Hold down to recover crouching.</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>291a27a1-971c-46b9-9947-912b13482b29</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>b42515eb-8c39-4e24-b02e-a0d9128c371a</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr">
         <is>
           <t>c4b1e1c8-3af0-4a69-bebd-86be82bc2f76</t>
         </is>
@@ -5971,17 +5992,17 @@
           <t>Continue with the Front Kick Series extentions.</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>108b9ae9-8c48-4c71-83d0-8aac669b145c</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>18f95788-72a3-4665-b1b3-391731511167</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
+      <c r="AA65" t="inlineStr">
         <is>
           <t>c4b1e1c8-3af0-4a69-bebd-86be82bc2f76</t>
         </is>
@@ -6073,17 +6094,17 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>94aab487-00a2-4e41-994f-c76a04d7e5d2</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>548dd05b-f985-4d7b-b2dd-d60224d695c5</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
+      <c r="AA66" t="inlineStr">
         <is>
           <t>c4b1e1c8-3af0-4a69-bebd-86be82bc2f76</t>
         </is>
@@ -6092,27 +6113,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>f+2 [~5]</t>
+          <t>f+2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>f+2 [~5]</t>
+          <t>f+2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>df+1+2 [~5]</t>
+          <t>df+1+2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Charging Strike [Tag]</t>
+          <t>Charging Strike</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Charging Strike [Tag]</t>
+          <t>Charging Strike</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6187,10 +6208,15 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
           <t>b5c67ae7-f1b6-4565-b4bc-1f0236bc1882</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>08792e9e-9271-4d20-8c67-a0aa97048dd6</t>
         </is>
@@ -6204,7 +6230,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>f+2 [~5]~d</t>
+          <t>f+2~d</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6214,7 +6240,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Charging Strike [Tag] – Strike Cancel</t>
+          <t>Charging Strike – Strike Cancel</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6267,17 +6293,17 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>e1947643-5386-4b51-8120-285066c0ad8d</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>5ba56f26-909b-44e7-8a46-0ceb35c518ea</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>b5c67ae7-f1b6-4565-b4bc-1f0236bc1882</t>
         </is>
@@ -6369,12 +6395,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>7252f468-d82c-418e-aa51-49e2353184fe</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>306972fa-ff55-4e89-8bfd-92579f25e9d2</t>
         </is>
@@ -6383,22 +6409,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>db+2 [~5]</t>
+          <t>db+2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>db+2 [~5]</t>
+          <t>db+2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Rock Shooter [Tag]</t>
+          <t>Rock Shooter</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rock Shooter [Tag]</t>
+          <t>Rock Shooter</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6473,10 +6499,15 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
           <t>645af39c-664a-4747-8cdb-1ab919a05c35</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>133cbb27-096b-444e-84d4-9a4cdd5a0351</t>
         </is>
@@ -6578,12 +6609,12 @@
           <t>GB</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>273d7b77-cd5c-460e-8e15-78a1bce8ceac</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>ee9779f2-ca89-47b3-a40c-5039e4bfa7cd</t>
         </is>
@@ -6670,17 +6701,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>079b898d-43f3-4e66-9a3a-2d2a5bd4c26c</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>574e1dec-96f0-439a-9afe-47bb00aa1649</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>273d7b77-cd5c-460e-8e15-78a1bce8ceac</t>
         </is>
@@ -6767,17 +6798,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>8f86d771-2b51-475f-bf80-3ec819609f97</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>cacc1179-8087-4375-be0b-6f0e97e67188</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>273d7b77-cd5c-460e-8e15-78a1bce8ceac</t>
         </is>
@@ -6869,17 +6900,17 @@
           <t>Continue with the Front Kick Series extentions.</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>78238c2f-f4df-4f80-a6e5-ce8a992f8222</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>65a72baf-1151-46c6-abc3-942d085fef4c</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>8f86d771-2b51-475f-bf80-3ec819609f97</t>
         </is>
@@ -6971,17 +7002,17 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>47ca4a25-db9d-4e9e-bca5-5d6740954e1e</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>e3f26352-5438-4ec9-abde-867d4e16c226</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
+      <c r="AA75" t="inlineStr">
         <is>
           <t>8f86d771-2b51-475f-bf80-3ec819609f97</t>
         </is>
@@ -7073,17 +7104,17 @@
           <t>Continue with the Leg Cutter Series extentions.; Hold down to recover crouching.</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>99980675-1530-4118-b7cf-dd4b4955e1d4</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>5d4ac6fb-7ebc-4618-85c4-609e55fa6daa</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>273d7b77-cd5c-460e-8e15-78a1bce8ceac</t>
         </is>
@@ -7185,12 +7216,12 @@
           <t>RC MSc</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>2917757d-e300-4d9b-bf25-8aefcfb969cf</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>450123d3-d1ad-4317-a5f9-809bcb1ebdd1</t>
         </is>
@@ -7287,12 +7318,12 @@
           <t>Also reverses high &amp;amp; mid punches.</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>5928043d-e8cf-48ad-aeca-749ccee1fc3d</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>106a03c2-2477-4ae4-b278-cbb7d7e3a1e5</t>
         </is>
@@ -7301,22 +7332,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>b+3 [~5]</t>
+          <t>b+3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>b+3 [~5]</t>
+          <t>b+3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Back Flip [Tag]</t>
+          <t>Back Flip</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Back Flip [Tag]</t>
+          <t>Back Flip</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7391,10 +7422,15 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
           <t>adc04340-7ea4-4d6a-bfa4-7643495e44fa</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>38259a37-ad1a-4674-b7db-29d07126bcdb</t>
         </is>
@@ -7403,22 +7439,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>– 2 [~5]</t>
+          <t>– 2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>b+3 [~5],2 [~5]</t>
+          <t>b+3,2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>– Charging Strike [Tag]</t>
+          <t>– Charging Strike</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Back Flip [Tag] – Charging Strike [Tag]</t>
+          <t>Back Flip – Charging Strike</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7488,15 +7524,20 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
           <t>977f11b2-1683-4e8a-84b0-14e3c66e23c1</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>e793aa8e-5d9f-4c09-bb90-826f5e2d2432</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>adc04340-7ea4-4d6a-bfa4-7643495e44fa</t>
         </is>
@@ -7510,7 +7551,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>b+3 [~5],4</t>
+          <t>b+3,4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7520,7 +7561,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Back Flip [Tag] – Leg Cutter</t>
+          <t>Back Flip – Leg Cutter</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7588,17 +7629,17 @@
           <t>Continue with the Leg Cutter Series extentions.; Hold down to recover crouching.</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>2e3121bd-b400-4f19-8ec0-77c63d3aa63f</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>e961d417-9176-49cf-9fcd-a30be9d7f625</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>adc04340-7ea4-4d6a-bfa4-7643495e44fa</t>
         </is>
@@ -7695,12 +7736,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>a3d8bafb-20d5-427f-8a3f-97752e2074d0</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>c91be3e0-8c63-4066-bef6-9b6a9b59c702</t>
         </is>
@@ -7797,12 +7838,12 @@
           <t>Keep holding forward for a second spin at which time it will hit mid for 40 damage.</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>bf03ba4f-212b-4d2b-bdbb-6b88a083a1b0</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>659dcd92-c91f-4419-a0b6-6be98c448adb</t>
         </is>
@@ -7874,17 +7915,17 @@
           <t>h-</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>4ee55c8c-884e-4636-9689-90463a04da21</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>42d2f3fc-6c31-4618-a68b-d43976ce85d1</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
+      <c r="AA84" t="inlineStr">
         <is>
           <t>bf03ba4f-212b-4d2b-bdbb-6b88a083a1b0</t>
         </is>
@@ -7986,12 +8027,12 @@
           <t>Hold down to recover crouching.</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>87f96bbc-70c7-497a-8030-873f2443e3f9</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>f07c06d6-7943-4fd8-a77a-a2dfc00f1a9a</t>
         </is>
@@ -8078,17 +8119,17 @@
           <t>LmM</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>e07b2a6d-68bd-400b-b261-f0af6e342c30</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>34173df9-c2d4-45e5-a001-2b7197e7bd13</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>87f96bbc-70c7-497a-8030-873f2443e3f9</t>
         </is>
@@ -8180,17 +8221,17 @@
           <t>Continue with the White Heron Series extentions.</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>e4deee7e-39bf-472e-b24d-3045541002ae</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>17f8fb03-1945-4295-a843-2f9fa0bfb4fe</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>87f96bbc-70c7-497a-8030-873f2443e3f9</t>
         </is>
@@ -8282,17 +8323,17 @@
           <t>Continue with the Leg Cutter Series extentions.; Hold down to recover crouching.</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="Y88" t="inlineStr">
         <is>
           <t>60f0f6c9-5f5f-46c8-af9b-f0ac25841f2f</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>193e03e1-e889-4f67-804c-6c3c0d7e3a76</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>87f96bbc-70c7-497a-8030-873f2443e3f9</t>
         </is>
@@ -8379,17 +8420,17 @@
           <t>LLmM</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>05b6e9b4-34c4-409a-b1b3-d747c25979e7</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>313bcef3-457c-42b9-8c20-b2c8c04e7050</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>60f0f6c9-5f5f-46c8-af9b-f0ac25841f2f</t>
         </is>
@@ -8481,17 +8522,17 @@
           <t>Continue with the White Heron Series extentions.</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>0fbdf5e4-e4b4-4495-8a52-517f52958af8</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>22b9444f-1171-4857-8928-0d5a1f2ace89</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>60f0f6c9-5f5f-46c8-af9b-f0ac25841f2f</t>
         </is>
@@ -8583,17 +8624,17 @@
           <t>Continue with the Leg Cutter Series extentions.; Hold down to recover crouching.</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>7ca8b6f6-6df0-4c1e-9773-f8ac11996479</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>46d7ee3a-91ce-441b-b84c-67779e657b26</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>87f96bbc-70c7-497a-8030-873f2443e3f9</t>
         </is>
@@ -8680,17 +8721,17 @@
           <t>LLLmM</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>03735048-2331-4b35-b17d-c1d27b311834</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>1bf00dac-706d-45d1-b8bb-9e22571db4cb</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>7ca8b6f6-6df0-4c1e-9773-f8ac11996479</t>
         </is>
@@ -8782,17 +8823,17 @@
           <t>Continue with the White Heron Series extentions.</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>7d702307-e1e4-46a8-8b69-f1a4a1532fc4</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>6424df2e-b7a1-4439-826a-6061bc257327</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>7ca8b6f6-6df0-4c1e-9773-f8ac11996479</t>
         </is>
@@ -8884,12 +8925,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>9bfd5dd2-0290-4cec-95e1-30b2484bb836</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>2b59fe95-7f77-452f-b5b5-d01b153d03e9</t>
         </is>
@@ -8986,12 +9027,12 @@
           <t>MS FCDc</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>665fd494-eb27-4c33-8cdc-bbec70c3d7a3</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>35601885-50c6-41bd-b7db-8d55e04ef907</t>
         </is>
@@ -9083,12 +9124,12 @@
           <t>mM</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>1b6735ff-2ca6-4df0-8bcb-a6de9880de67</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>6ec335b4-27db-4db6-982e-449d3ea5d154</t>
         </is>
@@ -9185,12 +9226,12 @@
           <t>JG GB</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>45767d62-7ddc-4a5f-995f-c127870af649</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>7c04089b-6f4d-463f-a54b-53ac436589c0</t>
         </is>
@@ -9287,12 +9328,12 @@
           <t>mmmm</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>589ce949-7bcd-452c-a9bc-11f3f5527600</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>955f570d-1406-489e-87cb-9dde22cfd042</t>
         </is>
@@ -9349,12 +9390,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>b300c6bb-bf79-49af-8aff-364141cb3fdf</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>2f8f34b5-2eb1-443d-9d08-0cb569531344</t>
         </is>
@@ -9406,12 +9447,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>16572512-8164-4f6b-b991-6b4771d87d36</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>5fdd3e28-3cc6-4a59-81e9-c413a707b973</t>
         </is>
@@ -9543,20 +9584,25 @@
       </c>
       <c r="X103" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y103" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y103" s="1" t="inlineStr">
+      <c r="Z103" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z103" s="1" t="inlineStr">
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA103" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9638,12 +9684,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>63a9ad87-39fa-4f29-b364-ea6c9f102807</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>25e46cb3-2698-4880-9c2f-9b336eff72c5</t>
         </is>
@@ -9775,20 +9821,25 @@
       </c>
       <c r="X107" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y107" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y107" s="1" t="inlineStr">
+      <c r="Z107" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z107" s="1" t="inlineStr">
+      <c r="AA107" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA107" s="1" t="inlineStr">
+      <c r="AB107" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9830,12 +9881,12 @@
           <t>mhmmmlmlmm</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>fcd205b6-5f94-4cfd-a61b-4cc522dbe599</t>
         </is>
       </c>
-      <c r="AA108" t="inlineStr">
+      <c r="AB108" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9877,12 +9928,12 @@
           <t>mhmmmlhhlh</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>91ec0924-2220-448a-88fb-9b64f00b6f0c</t>
         </is>
       </c>
-      <c r="AA109" t="inlineStr">
+      <c r="AB109" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -9924,12 +9975,12 @@
           <t>mhmm</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>77355c32-3a7d-4d9f-8a8d-7ff03658cb77</t>
         </is>
       </c>
-      <c r="AA110" t="inlineStr">
+      <c r="AB110" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/jun_step7.xlsx
+++ b/sources/jun_step7.xlsx
@@ -928,6 +928,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>c3fb2b44-9abc-4fc9-8f10-b2e01504275a</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>c3fb2b44-9abc-4fc9-8f10-b2e01504275a</t>
@@ -990,6 +995,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4e122e09-243f-49b9-96ea-c109b7d9a02f</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr">
         <is>
           <t>4e122e09-243f-49b9-96ea-c109b7d9a02f</t>
@@ -1050,6 +1060,11 @@
       <c r="U9" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>30e2beaa-6d7c-42d2-8397-096837f7826d</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -9881,6 +9896,11 @@
           <t>mhmmmlmlmm</t>
         </is>
       </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>fcd205b6-5f94-4cfd-a61b-4cc522dbe599</t>
+        </is>
+      </c>
       <c r="Z108" t="inlineStr">
         <is>
           <t>fcd205b6-5f94-4cfd-a61b-4cc522dbe599</t>
@@ -9928,6 +9948,11 @@
           <t>mhmmmlhhlh</t>
         </is>
       </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>91ec0924-2220-448a-88fb-9b64f00b6f0c</t>
+        </is>
+      </c>
       <c r="Z109" t="inlineStr">
         <is>
           <t>91ec0924-2220-448a-88fb-9b64f00b6f0c</t>
@@ -9973,6 +9998,11 @@
       <c r="S110" t="inlineStr">
         <is>
           <t>mhmm</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>77355c32-3a7d-4d9f-8a8d-7ff03658cb77</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
